--- a/sheets/민요/검수/농부가.xlsx
+++ b/sheets/민요/검수/농부가.xlsx
@@ -4,14 +4,14 @@
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
     <sheet name="정간목록" sheetId="2" r:id="rId2"/>
-    <sheet name="악보 1" sheetId="3" r:id="rId3"/>
+    <sheet name="악보" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="맑은 고딕"/>
@@ -20,6 +20,26 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
     </font>
@@ -50,7 +70,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -73,11 +93,71 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -96,6 +176,33 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3102,8 +3209,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:Q14"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
@@ -3122,892 +3233,813 @@
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">농부가 — 민요채보-1/농부가.png</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5줄</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4줄</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3줄</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="N2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2줄</t>
-        </is>
-      </c>
-      <c r="O2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="P2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1줄</t>
-        </is>
-      </c>
-      <c r="Q2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰
-潢</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B2">
+        <is>
+          <t xml:space="preserve">농부가</t>
+        </is>
+      </c>
+      <c s="8" r="C2"/>
+      <c s="8" r="D2"/>
+      <c s="8" r="E2"/>
+      <c s="8" r="F2"/>
+      <c s="8" r="G2"/>
+      <c s="8" r="H2"/>
+      <c s="8" r="I2"/>
+      <c s="8" r="J2"/>
+      <c s="8" r="K2"/>
+      <c s="8" r="L2"/>
+      <c s="8" r="M2"/>
+      <c s="8" r="N2"/>
+      <c s="8" r="O2"/>
+      <c s="8" r="P2"/>
+      <c s="8" r="Q2"/>
+    </row>
+    <row r="3" ht="56" customHeight="1">
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰
+潢</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">각</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">버</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">거</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">정</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰
-潢</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="L3" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰
+潢</t>
+        </is>
+      </c>
+      <c r="M3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">여</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N3" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="O3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">상</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="P3" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q3" s="2" t="inlineStr">
+      <c r="Q3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
+    <row r="4" ht="56" customHeight="1">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="C4" s="14"/>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="E4" s="14"/>
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="G4" s="14"/>
+      <c r="H4" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="I4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J4" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">산</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰
-潢</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="L4" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰
+潢</t>
+        </is>
+      </c>
+      <c r="M4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">보</t>
         </is>
       </c>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="N4" s="12"/>
+      <c r="O4" s="14"/>
+      <c r="P4" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="Q4" s="2"/>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="Q4" s="14"/>
+    </row>
+    <row r="5" ht="56" customHeight="1">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">농</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">성</t>
         </is>
       </c>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰
-潢</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="F5" s="12"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="15"/>
+      <c r="L5" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰
+潢</t>
+        </is>
+      </c>
+      <c r="M5" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">농</t>
         </is>
       </c>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2"/>
-      <c r="P5" s="2"/>
-      <c r="Q5" s="2"/>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰
-潢</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="N5" s="12"/>
+      <c r="O5" s="15"/>
+      <c r="P5" s="12"/>
+      <c r="Q5" s="15"/>
+    </row>
+    <row r="6" ht="56" customHeight="1">
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰
+潢</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">부</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰
-潢</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰
+潢</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G6" s="13"/>
+      <c r="H6" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="I6" s="13"/>
+      <c r="J6" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">／
 汰</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰
-潢</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="L6" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰
+潢</t>
+        </is>
+      </c>
+      <c r="M6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">부</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N6" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">시</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P6" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr">
+      <c r="Q6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰
-潢</t>
-        </is>
-      </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰
-潢</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
+    <row r="7" ht="56" customHeight="1">
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰
+潢</t>
+        </is>
+      </c>
+      <c r="C7" s="14"/>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰
+潢</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">산</t>
         </is>
       </c>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="F7" s="12"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="14"/>
+      <c r="J7" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
       </c>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="L7" s="12"/>
+      <c r="M7" s="14"/>
+      <c r="N7" s="12"/>
+      <c r="O7" s="14"/>
+      <c r="P7" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰
-潢</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="Q7" s="14"/>
+    </row>
+    <row r="8" ht="56" customHeight="1">
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰
+潢</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">신</t>
         </is>
       </c>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="F8" s="12"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K8" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">테</t>
         </is>
       </c>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2"/>
-      <c r="Q8" s="2"/>
-    </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰
-潢</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="L8" s="12"/>
+      <c r="M8" s="15"/>
+      <c r="N8" s="12"/>
+      <c r="O8" s="15"/>
+      <c r="P8" s="12"/>
+      <c r="Q8" s="15"/>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰
+潢</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">한</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">팔</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">남</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰
-潢</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="H9" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰
+潢</t>
+        </is>
+      </c>
+      <c r="I9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">실</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰
-潢</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="J9" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰
+潢</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">남</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰
-潢</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="L9" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰
+潢</t>
+        </is>
+      </c>
+      <c r="M9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N9" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰
-潢</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
+      <c r="P9" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰
+潢</t>
+        </is>
+      </c>
+      <c r="Q9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">디</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰
-潢</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
+    <row r="10" ht="56" customHeight="1">
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰
+潢</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">소리를</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰
-潢</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰
+潢</t>
+        </is>
+      </c>
+      <c r="E10" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
-潢</t>
-        </is>
-      </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
-潢</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
+潢</t>
+          </r>
+        </is>
+      </c>
+      <c r="G10" s="14"/>
+      <c r="H10" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
+潢</t>
+          </r>
+        </is>
+      </c>
+      <c r="I10" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">부</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰
-潢</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="J10" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰
+潢</t>
+        </is>
+      </c>
+      <c r="K10" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰
-潢</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="L10" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰
+潢</t>
+        </is>
+      </c>
+      <c r="M10" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
       </c>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="N10" s="12"/>
+      <c r="O10" s="14"/>
+      <c r="P10" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q10" s="2" t="inlineStr">
+      <c r="Q10" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">허</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
+    <row r="11" ht="56" customHeight="1">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="C11" s="15"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="I11" s="15"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="15"/>
+      <c r="L11" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="M11" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">말</t>
         </is>
       </c>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2"/>
-      <c r="Q11" s="2"/>
-    </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰
-潢</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="N11" s="12"/>
+      <c r="O11" s="15"/>
+      <c r="P11" s="12"/>
+      <c r="Q11" s="15"/>
+    </row>
+    <row r="12" ht="56" customHeight="1">
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰
+潢</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">걸</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
       </c>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰
-潢</t>
-        </is>
-      </c>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰
-潢</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="F12" s="12"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="13"/>
+      <c r="J12" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰
+潢</t>
+        </is>
+      </c>
+      <c r="K12" s="13"/>
+      <c r="L12" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰
+潢</t>
+        </is>
+      </c>
+      <c r="M12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">들어</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="N12" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="O12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰
-潢</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
+      <c r="P12" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰
+潢</t>
+        </is>
+      </c>
+      <c r="Q12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">여</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰
-潢</t>
-        </is>
-      </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰
-潢</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+    <row r="13" ht="56" customHeight="1">
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰
+潢</t>
+        </is>
+      </c>
+      <c r="C13" s="14"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰
+潢</t>
+        </is>
+      </c>
+      <c r="G13" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">걸</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰
-潢</t>
-        </is>
-      </c>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="H13" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰
+潢</t>
+        </is>
+      </c>
+      <c r="I13" s="14"/>
+      <c r="J13" s="12"/>
+      <c r="K13" s="14"/>
+      <c r="L13" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="M13" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">보</t>
         </is>
       </c>
-      <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
-      <c r="P13" s="2" t="inlineStr">
+      <c r="N13" s="12"/>
+      <c r="O13" s="14"/>
+      <c r="P13" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="Q13" s="2" t="inlineStr">
+      <c r="Q13" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">주</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
+    <row r="14" ht="56" customHeight="1">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="D14" s="12"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">여</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H14" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="I14" s="15"/>
+      <c r="J14" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="K14" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="L14" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="M14" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">소</t>
         </is>
       </c>
-      <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
-      <c r="P14" s="2" t="inlineStr">
+      <c r="N14" s="12"/>
+      <c r="O14" s="15"/>
+      <c r="P14" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="Q14" s="2" t="inlineStr">
+      <c r="Q14" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">우</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:Q2"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" scale="76"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/농부가.xlsx
+++ b/sheets/민요/검수/농부가.xlsx
@@ -255,11 +255,7 @@
           <t xml:space="preserve">쪽</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">197</t>
-        </is>
-      </c>
+      <c r="B5" s="4"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -3807,10 +3803,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s=""/>
-      <c r="B1" s="">
-        <v>0</v>
-      </c>
+      <c r="A1" s="0"/>
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
@@ -4654,6 +4647,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="87"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="86"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/농부가.xlsx
+++ b/sheets/민요/검수/농부가.xlsx
@@ -409,7 +409,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -697,12 +697,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|㴌汰</t>
+          <t xml:space="preserve">–|㴌汰</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 㴌汰</t>
         </is>
       </c>
@@ -851,12 +851,12 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I10" s="2"/>
@@ -886,13 +886,13 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰|―㴌</t>
+          <t xml:space="preserve">汰|–㴌</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-―㴌</t>
+–㴌</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I34" s="2"/>
@@ -1985,12 +1985,12 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|汰</t>
+          <t xml:space="preserve">–|汰</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
@@ -2068,13 +2068,13 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰潢|―</t>
+          <t xml:space="preserve">汰潢|–</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">汰潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -2647,12 +2647,12 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|㴌</t>
+          <t xml:space="preserve">–|㴌</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 㴌</t>
         </is>
       </c>
@@ -2896,12 +2896,12 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|㴌</t>
+          <t xml:space="preserve">–|㴌</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 㴌</t>
         </is>
       </c>
@@ -3018,12 +3018,12 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I66" s="2"/>
@@ -3092,13 +3092,13 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―㴌</t>
+          <t xml:space="preserve">潢|–㴌</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―㴌</t>
+–㴌</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
@@ -3211,13 +3211,13 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌湳|―</t>
+          <t xml:space="preserve">㴌湳|–</t>
         </is>
       </c>
       <c r="H71" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌湳
-―</t>
+–</t>
         </is>
       </c>
       <c r="I71" s="3" t="inlineStr">
@@ -3411,13 +3411,13 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―</t>
+          <t xml:space="preserve">南|–</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
@@ -3650,12 +3650,12 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I82" s="2"/>
@@ -3685,13 +3685,13 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南南|―</t>
+          <t xml:space="preserve">南南|–</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南南
-―</t>
+–</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -3916,7 +3916,7 @@
       </c>
       <c r="D4" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 㴌</t>
         </is>
       </c>
@@ -3971,7 +3971,7 @@
       <c r="B5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="H5" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="D7" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E7" s="9"/>
@@ -4138,7 +4138,7 @@
       <c r="H7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">汰潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="I7" s="9" t="inlineStr">
@@ -4160,7 +4160,7 @@
       <c r="M7" s="12"/>
       <c r="N7" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 㴌汰</t>
         </is>
       </c>
@@ -4241,7 +4241,7 @@
       <c r="D9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―㴌</t>
+–㴌</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
@@ -4328,7 +4328,7 @@
       </c>
       <c r="F10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 㴌</t>
         </is>
       </c>
@@ -4379,7 +4379,7 @@
       <c r="A11" s="0"/>
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C11" s="10"/>
@@ -4415,7 +4415,7 @@
       </c>
       <c r="J11" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K11" s="10"/>
@@ -4432,7 +4432,7 @@
       </c>
       <c r="N11" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O11" s="10"/>
@@ -4442,7 +4442,7 @@
       <c r="B12" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南南
-―</t>
+–</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -4453,7 +4453,7 @@
       <c r="D12" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌湳
-―</t>
+–</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
@@ -4504,7 +4504,7 @@
       <c r="N12" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-―㴌</t>
+–㴌</t>
         </is>
       </c>
       <c r="O12" s="8" t="inlineStr">
@@ -4583,7 +4583,7 @@
       <c r="A14" s="0"/>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>

--- a/sheets/민요/검수/농부가.xlsx
+++ b/sheets/민요/검수/농부가.xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3807,96 +3848,96 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">농부가</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">각</t>
         </is>
       </c>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 汰</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">어농</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="F3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 㴌</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">전라</t>
         </is>
       </c>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="H3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="I3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="J3" s="17" t="inlineStr">
+      <c r="J3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 㴌</t>
         </is>
       </c>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="K3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">여보</t>
         </is>
       </c>
-      <c r="L3" s="17" t="inlineStr">
+      <c r="L3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M3" s="8" t="inlineStr">
+      <c r="M3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">상</t>
         </is>
       </c>
-      <c r="N3" s="17" t="inlineStr">
+      <c r="N3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O3" s="8" t="inlineStr">
+      <c r="O3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -3904,207 +3945,207 @@
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無^</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">기</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 㴌</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">부</t>
         </is>
       </c>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 㴌</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">도라</t>
         </is>
       </c>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="I4" s="9"/>
-      <c r="J4" s="17" t="inlineStr">
+      <c r="I4" s="23"/>
+      <c r="J4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 㴌</t>
         </is>
       </c>
-      <c r="K4" s="9" t="inlineStr">
+      <c r="K4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">시요</t>
         </is>
       </c>
-      <c r="L4" s="17" t="inlineStr">
+      <c r="L4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="M4" s="9"/>
-      <c r="N4" s="17" t="inlineStr">
+      <c r="M4" s="23"/>
+      <c r="N4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="O4" s="9"/>
+      <c r="O4" s="23"/>
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 –</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">경</t>
         </is>
       </c>
-      <c r="D5" s="18" t="inlineStr">
+      <c r="D5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="E5" s="13" t="inlineStr">
+      <c r="E5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">들</t>
         </is>
       </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 㴌</t>
         </is>
       </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="G5" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">하는</t>
         </is>
       </c>
-      <c r="H5" s="18" t="inlineStr">
+      <c r="H5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
-      <c r="I5" s="13" t="inlineStr">
+      <c r="I5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">후화</t>
         </is>
       </c>
-      <c r="J5" s="17" t="inlineStr">
+      <c r="J5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 㴌</t>
         </is>
       </c>
-      <c r="K5" s="10" t="inlineStr">
+      <c r="K5" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">농부</t>
         </is>
       </c>
-      <c r="L5" s="17" t="inlineStr">
+      <c r="L5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="M5" s="10"/>
-      <c r="N5" s="17" t="inlineStr">
+      <c r="M5" s="24"/>
+      <c r="N5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="O5" s="10"/>
+      <c r="O5" s="24"/>
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無^</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">정</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌^</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 㴌</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="G6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">데는</t>
         </is>
       </c>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I6" s="8" t="inlineStr">
+      <c r="I6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">농</t>
         </is>
       </c>
-      <c r="J6" s="17" t="inlineStr">
+      <c r="J6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 㴌</t>
         </is>
       </c>
-      <c r="K6" s="8" t="inlineStr">
+      <c r="K6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">님네</t>
         </is>
       </c>
-      <c r="L6" s="17" t="inlineStr">
+      <c r="L6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M6" s="8" t="inlineStr">
+      <c r="M6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="N6" s="17" t="inlineStr">
+      <c r="N6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="O6" s="8" t="inlineStr">
+      <c r="O6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -4112,114 +4153,114 @@
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">거리</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E7" s="9"/>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="E7" s="23"/>
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="G7" s="9"/>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="G7" s="23"/>
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰潢
 –</t>
         </is>
       </c>
-      <c r="I7" s="9" t="inlineStr">
+      <c r="I7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">부</t>
         </is>
       </c>
-      <c r="J7" s="17" t="inlineStr">
+      <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="K7" s="9"/>
-      <c r="L7" s="18" t="inlineStr">
+      <c r="K7" s="23"/>
+      <c r="L7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M7" s="12"/>
-      <c r="N7" s="17" t="inlineStr">
+      <c r="M7" s="27"/>
+      <c r="N7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 㴌汰</t>
         </is>
       </c>
-      <c r="O7" s="9"/>
+      <c r="O7" s="23"/>
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無^
 △</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
-      <c r="D8" s="18" t="inlineStr">
+      <c r="D8" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E8" s="13"/>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="E8" s="26"/>
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="G8" s="10"/>
-      <c r="H8" s="18" t="inlineStr">
+      <c r="G8" s="24"/>
+      <c r="H8" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I8" s="13" t="inlineStr">
+      <c r="I8" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">님</t>
         </is>
       </c>
-      <c r="J8" s="17" t="inlineStr">
+      <c r="J8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="K8" s="10"/>
-      <c r="L8" s="17" t="inlineStr">
+      <c r="K8" s="24"/>
+      <c r="L8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M8" s="10"/>
-      <c r="N8" s="17" t="inlineStr">
+      <c r="M8" s="24"/>
+      <c r="N8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 △</t>
         </is>
       </c>
-      <c r="O8" s="10" t="inlineStr">
+      <c r="O8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">허어</t>
         </is>
@@ -4227,76 +4268,76 @@
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 潢</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">너</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –㴌</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">상사</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 汰</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">신산</t>
         </is>
       </c>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I9" s="8" t="inlineStr">
+      <c r="I9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">말</t>
         </is>
       </c>
-      <c r="J9" s="17" t="inlineStr">
+      <c r="J9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 㴌</t>
         </is>
       </c>
-      <c r="K9" s="8" t="inlineStr">
+      <c r="K9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">이네</t>
         </is>
       </c>
-      <c r="L9" s="17" t="inlineStr">
+      <c r="L9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M9" s="8" t="inlineStr">
+      <c r="M9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">디</t>
         </is>
       </c>
-      <c r="N9" s="17" t="inlineStr">
+      <c r="N9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="O9" s="8" t="inlineStr">
+      <c r="O9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -4304,72 +4345,72 @@
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 姑</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">부렁</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 㴌</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">소리</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 㴌</t>
         </is>
       </c>
-      <c r="G10" s="9" t="inlineStr">
+      <c r="G10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I10" s="9" t="inlineStr">
+      <c r="I10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">들</t>
         </is>
       </c>
-      <c r="J10" s="17" t="inlineStr">
+      <c r="J10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 㴌</t>
         </is>
       </c>
-      <c r="K10" s="9" t="inlineStr">
+      <c r="K10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">말씀</t>
         </is>
       </c>
-      <c r="L10" s="17" t="inlineStr">
+      <c r="L10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="M10" s="9"/>
-      <c r="N10" s="17" t="inlineStr">
+      <c r="M10" s="23"/>
+      <c r="N10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="O10" s="9" t="inlineStr">
+      <c r="O10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">허</t>
         </is>
@@ -4377,137 +4418,137 @@
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="C11" s="24"/>
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="E11" s="10" t="inlineStr">
+      <c r="E11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">를</t>
         </is>
       </c>
-      <c r="F11" s="18" t="inlineStr">
+      <c r="F11" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="G11" s="13" t="inlineStr">
+      <c r="G11" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">비</t>
         </is>
       </c>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I11" s="10" t="inlineStr">
+      <c r="I11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="J11" s="17" t="inlineStr">
+      <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K11" s="10"/>
-      <c r="L11" s="17" t="inlineStr">
+      <c r="K11" s="24"/>
+      <c r="L11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="M11" s="10" t="inlineStr">
+      <c r="M11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="N11" s="17" t="inlineStr">
+      <c r="N11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O11" s="10"/>
+      <c r="O11" s="24"/>
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南南
 –</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">거리</t>
         </is>
       </c>
-      <c r="D12" s="18" t="inlineStr">
+      <c r="D12" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌湳
 –</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="E12" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">메기</t>
         </is>
       </c>
-      <c r="F12" s="18" t="inlineStr">
+      <c r="F12" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="G12" s="11" t="inlineStr">
+      <c r="G12" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">친</t>
         </is>
       </c>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="H12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I12" s="8" t="inlineStr">
+      <c r="I12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">요</t>
         </is>
       </c>
-      <c r="J12" s="17" t="inlineStr">
+      <c r="J12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="K12" s="8" t="inlineStr">
+      <c r="K12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">들어</t>
         </is>
       </c>
-      <c r="L12" s="17" t="inlineStr">
+      <c r="L12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M12" s="8" t="inlineStr">
+      <c r="M12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
-      <c r="N12" s="17" t="inlineStr">
+      <c r="N12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 –㴌</t>
         </is>
       </c>
-      <c r="O12" s="8" t="inlineStr">
+      <c r="O12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">여</t>
         </is>
@@ -4515,65 +4556,65 @@
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
       </c>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
       </c>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 㴌</t>
         </is>
       </c>
-      <c r="G13" s="9" t="inlineStr">
+      <c r="G13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">곳이</t>
         </is>
       </c>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I13" s="9"/>
-      <c r="J13" s="17" t="inlineStr">
+      <c r="I13" s="23"/>
+      <c r="J13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="K13" s="9" t="inlineStr">
+      <c r="K13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">보</t>
         </is>
       </c>
-      <c r="L13" s="17" t="inlineStr">
+      <c r="L13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="M13" s="9"/>
-      <c r="N13" s="17" t="inlineStr">
+      <c r="M13" s="23"/>
+      <c r="N13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="O13" s="9" t="inlineStr">
+      <c r="O13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">루</t>
         </is>
@@ -4581,61 +4622,61 @@
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="C14" s="24"/>
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無^</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E14" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">데</t>
         </is>
       </c>
-      <c r="F14" s="18" t="inlineStr">
+      <c r="F14" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="G14" s="13" t="inlineStr">
+      <c r="G14" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I14" s="10"/>
-      <c r="J14" s="17" t="inlineStr">
+      <c r="I14" s="24"/>
+      <c r="J14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K14" s="10" t="inlineStr">
+      <c r="K14" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">소</t>
         </is>
       </c>
-      <c r="L14" s="17" t="inlineStr">
+      <c r="L14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="M14" s="10"/>
-      <c r="N14" s="17" t="inlineStr">
+      <c r="M14" s="24"/>
+      <c r="N14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無^</t>
         </is>
       </c>
-      <c r="O14" s="10" t="inlineStr">
+      <c r="O14" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">우</t>
         </is>

--- a/sheets/민요/검수/농부가.xlsx
+++ b/sheets/민요/검수/농부가.xlsx
@@ -3827,26 +3827,26 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="60.41" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
       <c r="N2" s="20"/>
       <c r="O2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="60.41" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="60.41" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -3996,18 +3996,18 @@
       </c>
       <c r="L4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M4" s="23"/>
       <c r="N4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O4" s="23"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="60.41" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4065,18 +4065,18 @@
       </c>
       <c r="L5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M5" s="24"/>
       <c r="N5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O5" s="24"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="60.41" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="60.41" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="O7" s="23"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="60.41" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="60.41" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="60.41" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
       </c>
       <c r="L10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M10" s="23"/>
@@ -4416,7 +4416,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="60.41" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
       </c>
       <c r="O11" s="24"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="60.41" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="60.41" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
       </c>
       <c r="H13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I13" s="23"/>
@@ -4605,7 +4605,7 @@
       </c>
       <c r="L13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M13" s="23"/>
@@ -4620,7 +4620,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="60.41" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="H14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I14" s="24"/>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="L14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M14" s="24"/>

--- a/sheets/민요/검수/농부가.xlsx
+++ b/sheets/민요/검수/농부가.xlsx
@@ -3887,7 +3887,8 @@
       </c>
       <c r="E3" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">어농</t>
+          <t xml:space="preserve">어
+농</t>
         </is>
       </c>
       <c r="F3" s="21" t="inlineStr">
@@ -3898,7 +3899,8 @@
       </c>
       <c r="G3" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">전라</t>
+          <t xml:space="preserve">전
+라</t>
         </is>
       </c>
       <c r="H3" s="21" t="inlineStr">
@@ -3919,7 +3921,8 @@
       </c>
       <c r="K3" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">여보</t>
+          <t xml:space="preserve">여
+보</t>
         </is>
       </c>
       <c r="L3" s="21" t="inlineStr">
@@ -3974,7 +3977,8 @@
       </c>
       <c r="G4" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">도라</t>
+          <t xml:space="preserve">도
+라</t>
         </is>
       </c>
       <c r="H4" s="21" t="inlineStr">
@@ -3991,7 +3995,8 @@
       </c>
       <c r="K4" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">시요</t>
+          <t xml:space="preserve">시
+요</t>
         </is>
       </c>
       <c r="L4" s="21" t="inlineStr">
@@ -4038,7 +4043,8 @@
       </c>
       <c r="G5" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">하는</t>
+          <t xml:space="preserve">하
+는</t>
         </is>
       </c>
       <c r="H5" s="25" t="inlineStr">
@@ -4049,7 +4055,8 @@
       </c>
       <c r="I5" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">후화</t>
+          <t xml:space="preserve">후
+화</t>
         </is>
       </c>
       <c r="J5" s="21" t="inlineStr">
@@ -4060,7 +4067,8 @@
       </c>
       <c r="K5" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">농부</t>
+          <t xml:space="preserve">농
+부</t>
         </is>
       </c>
       <c r="L5" s="21" t="inlineStr">
@@ -4106,7 +4114,8 @@
       </c>
       <c r="G6" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">데는</t>
+          <t xml:space="preserve">데
+는</t>
         </is>
       </c>
       <c r="H6" s="21" t="inlineStr">
@@ -4127,7 +4136,8 @@
       </c>
       <c r="K6" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">님네</t>
+          <t xml:space="preserve">님
+네</t>
         </is>
       </c>
       <c r="L6" s="21" t="inlineStr">
@@ -4161,7 +4171,8 @@
       </c>
       <c r="C7" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">거리</t>
+          <t xml:space="preserve">거
+리</t>
         </is>
       </c>
       <c r="D7" s="21" t="inlineStr">
@@ -4262,7 +4273,8 @@
       </c>
       <c r="O8" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">허어</t>
+          <t xml:space="preserve">허
+어</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4299,8 @@
       </c>
       <c r="E9" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">상사</t>
+          <t xml:space="preserve">상
+사</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr">
@@ -4298,7 +4311,8 @@
       </c>
       <c r="G9" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">신산</t>
+          <t xml:space="preserve">신
+산</t>
         </is>
       </c>
       <c r="H9" s="21" t="inlineStr">
@@ -4319,7 +4333,8 @@
       </c>
       <c r="K9" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">이네</t>
+          <t xml:space="preserve">이
+네</t>
         </is>
       </c>
       <c r="L9" s="21" t="inlineStr">
@@ -4353,7 +4368,8 @@
       </c>
       <c r="C10" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">부렁</t>
+          <t xml:space="preserve">부
+렁</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
@@ -4364,7 +4380,8 @@
       </c>
       <c r="E10" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">소리</t>
+          <t xml:space="preserve">소
+리</t>
         </is>
       </c>
       <c r="F10" s="21" t="inlineStr">
@@ -4396,7 +4413,8 @@
       </c>
       <c r="K10" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">말씀</t>
+          <t xml:space="preserve">말
+씀</t>
         </is>
       </c>
       <c r="L10" s="21" t="inlineStr">
@@ -4488,7 +4506,8 @@
       </c>
       <c r="C12" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">거리</t>
+          <t xml:space="preserve">거
+리</t>
         </is>
       </c>
       <c r="D12" s="25" t="inlineStr">
@@ -4499,7 +4518,8 @@
       </c>
       <c r="E12" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">메기</t>
+          <t xml:space="preserve">메
+기</t>
         </is>
       </c>
       <c r="F12" s="25" t="inlineStr">
@@ -4529,7 +4549,8 @@
       </c>
       <c r="K12" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">들어</t>
+          <t xml:space="preserve">들
+어</t>
         </is>
       </c>
       <c r="L12" s="21" t="inlineStr">
@@ -4584,7 +4605,8 @@
       </c>
       <c r="G13" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">곳이</t>
+          <t xml:space="preserve">곳
+이</t>
         </is>
       </c>
       <c r="H13" s="21" t="inlineStr">

--- a/sheets/민요/검수/농부가.xlsx
+++ b/sheets/민요/검수/농부가.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -47,6 +47,11 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -236,6 +241,24 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3874,7 +3897,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="C3" s="22" t="inlineStr">
+      <c r="C3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">각</t>
         </is>
@@ -3885,7 +3908,7 @@
 汰</t>
         </is>
       </c>
-      <c r="E3" s="22" t="inlineStr">
+      <c r="E3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">어
 농</t>
@@ -3897,7 +3920,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="G3" s="22" t="inlineStr">
+      <c r="G3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">전
 라</t>
@@ -3908,7 +3931,7 @@
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="I3" s="22" t="inlineStr">
+      <c r="I3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -3919,7 +3942,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="K3" s="22" t="inlineStr">
+      <c r="K3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">여
 보</t>
@@ -3930,7 +3953,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M3" s="22" t="inlineStr">
+      <c r="M3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">상</t>
         </is>
@@ -3940,7 +3963,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O3" s="22" t="inlineStr">
+      <c r="O3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -3953,7 +3976,7 @@
           <t xml:space="preserve">無^</t>
         </is>
       </c>
-      <c r="C4" s="23" t="inlineStr">
+      <c r="C4" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">기</t>
         </is>
@@ -3964,7 +3987,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="E4" s="23" t="inlineStr">
+      <c r="E4" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">부</t>
         </is>
@@ -3975,7 +3998,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="G4" s="23" t="inlineStr">
+      <c r="G4" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">도
 라</t>
@@ -3986,14 +4009,14 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="I4" s="23"/>
+      <c r="I4" s="30"/>
       <c r="J4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 㴌</t>
         </is>
       </c>
-      <c r="K4" s="23" t="inlineStr">
+      <c r="K4" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">시
 요</t>
@@ -4004,13 +4027,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M4" s="23"/>
+      <c r="M4" s="30"/>
       <c r="N4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O4" s="23"/>
+      <c r="O4" s="30"/>
     </row>
     <row r="5" ht="60.41" customHeight="1">
       <c r="A5" s="0"/>
@@ -4020,7 +4043,7 @@
 –</t>
         </is>
       </c>
-      <c r="C5" s="24" t="inlineStr">
+      <c r="C5" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">경</t>
         </is>
@@ -4030,7 +4053,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="E5" s="26" t="inlineStr">
+      <c r="E5" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">들</t>
         </is>
@@ -4041,7 +4064,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="G5" s="24" t="inlineStr">
+      <c r="G5" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">하
 는</t>
@@ -4053,7 +4076,7 @@
 汰</t>
         </is>
       </c>
-      <c r="I5" s="26" t="inlineStr">
+      <c r="I5" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">후
 화</t>
@@ -4065,7 +4088,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="K5" s="24" t="inlineStr">
+      <c r="K5" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">농
 부</t>
@@ -4076,13 +4099,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M5" s="24"/>
+      <c r="M5" s="31"/>
       <c r="N5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O5" s="24"/>
+      <c r="O5" s="31"/>
     </row>
     <row r="6" ht="60.41" customHeight="1">
       <c r="A6" s="0"/>
@@ -4091,7 +4114,7 @@
           <t xml:space="preserve">無^</t>
         </is>
       </c>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="C6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">정</t>
         </is>
@@ -4101,7 +4124,7 @@
           <t xml:space="preserve">㴌^</t>
         </is>
       </c>
-      <c r="E6" s="22" t="inlineStr">
+      <c r="E6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
@@ -4112,7 +4135,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="G6" s="22" t="inlineStr">
+      <c r="G6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">데
 는</t>
@@ -4123,7 +4146,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I6" s="22" t="inlineStr">
+      <c r="I6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">농</t>
         </is>
@@ -4134,7 +4157,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="K6" s="22" t="inlineStr">
+      <c r="K6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">님
 네</t>
@@ -4145,7 +4168,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M6" s="22" t="inlineStr">
+      <c r="M6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
@@ -4155,7 +4178,7 @@
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="O6" s="22" t="inlineStr">
+      <c r="O6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -4169,7 +4192,7 @@
 南</t>
         </is>
       </c>
-      <c r="C7" s="23" t="inlineStr">
+      <c r="C7" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">거
 리</t>
@@ -4180,20 +4203,20 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E7" s="23"/>
+      <c r="E7" s="30"/>
       <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="G7" s="23"/>
+      <c r="G7" s="30"/>
       <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰潢
 –</t>
         </is>
       </c>
-      <c r="I7" s="23" t="inlineStr">
+      <c r="I7" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">부</t>
         </is>
@@ -4203,20 +4226,20 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="K7" s="23"/>
+      <c r="K7" s="30"/>
       <c r="L7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M7" s="27"/>
+      <c r="M7" s="33"/>
       <c r="N7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 㴌汰</t>
         </is>
       </c>
-      <c r="O7" s="23"/>
+      <c r="O7" s="30"/>
     </row>
     <row r="8" ht="60.41" customHeight="1">
       <c r="A8" s="0"/>
@@ -4226,7 +4249,7 @@
 △</t>
         </is>
       </c>
-      <c r="C8" s="24" t="inlineStr">
+      <c r="C8" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
@@ -4236,19 +4259,19 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E8" s="26"/>
+      <c r="E8" s="32"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="G8" s="24"/>
+      <c r="G8" s="31"/>
       <c r="H8" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I8" s="26" t="inlineStr">
+      <c r="I8" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">님</t>
         </is>
@@ -4258,20 +4281,20 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="K8" s="24"/>
+      <c r="K8" s="31"/>
       <c r="L8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M8" s="24"/>
+      <c r="M8" s="31"/>
       <c r="N8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 △</t>
         </is>
       </c>
-      <c r="O8" s="24" t="inlineStr">
+      <c r="O8" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">허
 어</t>
@@ -4286,7 +4309,7 @@
 潢</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">너</t>
         </is>
@@ -4297,7 +4320,7 @@
 –㴌</t>
         </is>
       </c>
-      <c r="E9" s="22" t="inlineStr">
+      <c r="E9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">상
 사</t>
@@ -4309,7 +4332,7 @@
 汰</t>
         </is>
       </c>
-      <c r="G9" s="22" t="inlineStr">
+      <c r="G9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">신
 산</t>
@@ -4320,7 +4343,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I9" s="22" t="inlineStr">
+      <c r="I9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">말</t>
         </is>
@@ -4331,7 +4354,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="K9" s="22" t="inlineStr">
+      <c r="K9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">이
 네</t>
@@ -4342,7 +4365,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M9" s="22" t="inlineStr">
+      <c r="M9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">디</t>
         </is>
@@ -4352,7 +4375,7 @@
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="O9" s="22" t="inlineStr">
+      <c r="O9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -4366,7 +4389,7 @@
 姑</t>
         </is>
       </c>
-      <c r="C10" s="23" t="inlineStr">
+      <c r="C10" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">부
 렁</t>
@@ -4378,7 +4401,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="E10" s="23" t="inlineStr">
+      <c r="E10" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">소
 리</t>
@@ -4390,7 +4413,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="G10" s="23" t="inlineStr">
+      <c r="G10" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -4400,7 +4423,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I10" s="23" t="inlineStr">
+      <c r="I10" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">들</t>
         </is>
@@ -4411,7 +4434,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="K10" s="23" t="inlineStr">
+      <c r="K10" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">말
 씀</t>
@@ -4422,13 +4445,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M10" s="23"/>
+      <c r="M10" s="30"/>
       <c r="N10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="O10" s="23" t="inlineStr">
+      <c r="O10" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">허</t>
         </is>
@@ -4441,13 +4464,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C11" s="24"/>
+      <c r="C11" s="31"/>
       <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="E11" s="24" t="inlineStr">
+      <c r="E11" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">를</t>
         </is>
@@ -4457,7 +4480,7 @@
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="G11" s="26" t="inlineStr">
+      <c r="G11" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">비</t>
         </is>
@@ -4467,7 +4490,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I11" s="24" t="inlineStr">
+      <c r="I11" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -4477,14 +4500,14 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K11" s="24"/>
+      <c r="K11" s="31"/>
       <c r="L11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="M11" s="24" t="inlineStr">
+      <c r="M11" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -4494,7 +4517,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O11" s="24"/>
+      <c r="O11" s="31"/>
     </row>
     <row r="12" ht="60.41" customHeight="1">
       <c r="A12" s="0"/>
@@ -4504,7 +4527,7 @@
 –</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="C12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">거
 리</t>
@@ -4516,7 +4539,7 @@
 –</t>
         </is>
       </c>
-      <c r="E12" s="28" t="inlineStr">
+      <c r="E12" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">메
 기</t>
@@ -4527,7 +4550,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="G12" s="28" t="inlineStr">
+      <c r="G12" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">친</t>
         </is>
@@ -4537,7 +4560,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I12" s="22" t="inlineStr">
+      <c r="I12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">요</t>
         </is>
@@ -4547,7 +4570,7 @@
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="K12" s="22" t="inlineStr">
+      <c r="K12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">들
 어</t>
@@ -4558,7 +4581,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M12" s="22" t="inlineStr">
+      <c r="M12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
@@ -4569,7 +4592,7 @@
 –㴌</t>
         </is>
       </c>
-      <c r="O12" s="22" t="inlineStr">
+      <c r="O12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">여</t>
         </is>
@@ -4582,7 +4605,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C13" s="23" t="inlineStr">
+      <c r="C13" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
@@ -4592,7 +4615,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="E13" s="23" t="inlineStr">
+      <c r="E13" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
@@ -4603,7 +4626,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="G13" s="23" t="inlineStr">
+      <c r="G13" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">곳
 이</t>
@@ -4614,13 +4637,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I13" s="23"/>
+      <c r="I13" s="30"/>
       <c r="J13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="K13" s="23" t="inlineStr">
+      <c r="K13" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">보</t>
         </is>
@@ -4630,13 +4653,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M13" s="23"/>
+      <c r="M13" s="30"/>
       <c r="N13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="O13" s="23" t="inlineStr">
+      <c r="O13" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">루</t>
         </is>
@@ -4650,13 +4673,13 @@
 △</t>
         </is>
       </c>
-      <c r="C14" s="24"/>
+      <c r="C14" s="31"/>
       <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無^</t>
         </is>
       </c>
-      <c r="E14" s="24" t="inlineStr">
+      <c r="E14" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">데</t>
         </is>
@@ -4666,7 +4689,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="G14" s="26" t="inlineStr">
+      <c r="G14" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
@@ -4676,13 +4699,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I14" s="24"/>
+      <c r="I14" s="31"/>
       <c r="J14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K14" s="24" t="inlineStr">
+      <c r="K14" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">소</t>
         </is>
@@ -4692,13 +4715,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M14" s="24"/>
+      <c r="M14" s="31"/>
       <c r="N14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無^</t>
         </is>
       </c>
-      <c r="O14" s="24" t="inlineStr">
+      <c r="O14" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">우</t>
         </is>

--- a/sheets/민요/검수/농부가.xlsx
+++ b/sheets/민요/검수/농부가.xlsx
@@ -70,10 +70,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="solid">

--- a/sheets/민요/검수/농부가.xlsx
+++ b/sheets/민요/검수/농부가.xlsx
@@ -3845,6 +3845,9 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -3863,10 +3866,10 @@
     <col min="15" max="15" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60.41" customHeight="1">
+    <row r="2" ht="60.61" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3887,7 +3890,7 @@
       <c r="N2" s="20"/>
       <c r="O2" s="20"/>
     </row>
-    <row r="3" ht="60.41" customHeight="1">
+    <row r="3" ht="90.2" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3966,7 +3969,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="60.41" customHeight="1">
+    <row r="4" ht="90.2" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4032,7 +4035,7 @@
       </c>
       <c r="O4" s="30"/>
     </row>
-    <row r="5" ht="60.41" customHeight="1">
+    <row r="5" ht="90.2" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4104,7 +4107,7 @@
       </c>
       <c r="O5" s="31"/>
     </row>
-    <row r="6" ht="60.41" customHeight="1">
+    <row r="6" ht="90.2" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4181,7 +4184,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="60.41" customHeight="1">
+    <row r="7" ht="90.2" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4238,7 +4241,7 @@
       </c>
       <c r="O7" s="30"/>
     </row>
-    <row r="8" ht="60.41" customHeight="1">
+    <row r="8" ht="90.2" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4298,7 +4301,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="60.41" customHeight="1">
+    <row r="9" ht="90.2" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -4378,7 +4381,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="60.41" customHeight="1">
+    <row r="10" ht="90.2" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -4454,7 +4457,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="60.41" customHeight="1">
+    <row r="11" ht="90.2" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -4516,7 +4519,7 @@
       </c>
       <c r="O11" s="31"/>
     </row>
-    <row r="12" ht="60.41" customHeight="1">
+    <row r="12" ht="90.2" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -4595,7 +4598,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="60.41" customHeight="1">
+    <row r="13" ht="90.2" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -4662,7 +4665,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="60.41" customHeight="1">
+    <row r="14" ht="90.2" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -4730,6 +4733,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="86"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="66"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/농부가.xlsx
+++ b/sheets/민요/검수/농부가.xlsx
@@ -3850,26 +3850,26 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="12" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="12" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60.61" customHeight="true">
+    <row r="2" ht="56.34" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
       <c r="N2" s="20"/>
       <c r="O2" s="20"/>
     </row>
-    <row r="3" ht="90.2" customHeight="true">
+    <row r="3" ht="83.81" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="90.2" customHeight="true">
+    <row r="4" ht="83.81" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="O4" s="30"/>
     </row>
-    <row r="5" ht="90.2" customHeight="true">
+    <row r="5" ht="83.81" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
       </c>
       <c r="O5" s="31"/>
     </row>
-    <row r="6" ht="90.2" customHeight="true">
+    <row r="6" ht="83.81" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4184,7 +4184,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="90.2" customHeight="true">
+    <row r="7" ht="83.81" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4241,7 +4241,7 @@
       </c>
       <c r="O7" s="30"/>
     </row>
-    <row r="8" ht="90.2" customHeight="true">
+    <row r="8" ht="83.81" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4301,7 +4301,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="90.2" customHeight="true">
+    <row r="9" ht="83.81" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="90.2" customHeight="true">
+    <row r="10" ht="83.81" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="90.2" customHeight="true">
+    <row r="11" ht="83.81" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
       </c>
       <c r="O11" s="31"/>
     </row>
-    <row r="12" ht="90.2" customHeight="true">
+    <row r="12" ht="83.81" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="90.2" customHeight="true">
+    <row r="13" ht="83.81" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="90.2" customHeight="true">
+    <row r="14" ht="83.81" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -4733,6 +4733,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="66"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="71"/>
 </worksheet>
 </file>